--- a/results/phase1_summary.xlsx
+++ b/results/phase1_summary.xlsx
@@ -481,33 +481,35 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>14389.33424756786</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>12627.95142527504</v>
+        <v>12768.65945763432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>C108</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14596.1650660543</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11414.99902326231</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>C109</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>12.55555555555556</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12064.2486358475</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10939.08214623804</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>C105</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>10.77777777777778</v>
+        <v>12.44444444444444</v>
       </c>
     </row>
     <row r="3">
@@ -517,32 +519,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6240.148900605343</v>
+        <v>6077.544745828163</v>
       </c>
       <c r="C3" t="n">
-        <v>5134.683621817112</v>
+        <v>5126.163780499669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>C208</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5283.234745642261</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4972.294963558592</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>C206</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4392.712879494148</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3660.83110722045</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C201</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -570,10 +572,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>17110.48270638082</v>
+        <v>18789.32564040475</v>
       </c>
       <c r="G4" t="n">
-        <v>13408.90087252276</v>
+        <v>14426.56252083727</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -581,7 +583,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>15.33333333333333</v>
+        <v>16.91666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -596,21 +598,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5500.042990675601</v>
+        <v>4271.161034760979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R211</t>
+          <t>R208</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.727272727272727</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="F5" t="n">
-        <v>5264.699233347286</v>
+        <v>5234.323302329899</v>
       </c>
       <c r="G5" t="n">
-        <v>4192.018395355964</v>
+        <v>4304.29987002672</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -618,7 +620,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.727272727272727</v>
+        <v>3.636363636363636</v>
       </c>
     </row>
     <row r="6">
@@ -646,18 +648,18 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16997.89967066366</v>
+        <v>19888.98947731833</v>
       </c>
       <c r="G6" t="n">
-        <v>13610.71675456563</v>
+        <v>16797.59302944587</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RC104</t>
+          <t>RC108</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="7">
@@ -672,29 +674,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8601.013303073547</v>
+        <v>7052.221862921664</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RC202</t>
+          <t>RC207</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>2.875</v>
       </c>
       <c r="F7" t="n">
-        <v>6035.759265810129</v>
+        <v>6548.308473535923</v>
       </c>
       <c r="G7" t="n">
-        <v>4472.288968880614</v>
+        <v>5591.555194414775</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>RC208</t>
+          <t>RC204</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.125</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
